--- a/paper/source_data/fig2_source_data.xlsx
+++ b/paper/source_data/fig2_source_data.xlsx
@@ -497,11 +497,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Fig. 2 | Retinal and clinical data of the same person share information in one BRAN embedding.**
-**a**, Same-person retrieval between retinal and clinical shared-block states in 1,924 AI-READI development participants (point estimates, no intervals). † Earlier BRAN checkpoint, the retained model is PLACEHOLDER. CCA was not age-adjusted, so the advantage over raw CCA holds only before age adjustment. With age removed MRR was 0.049, above all 256 age-matched shuffles (95th percentile 0.020, one-sided permutation P ≤ 0.004, the smallest attainable). CCA, canonical correlation analysis.
-**b**, Native-head AUROC for 26 self-reported conditions from clinical-only and retinal-only inputs in development participants with all three routes (n withheld by the source). Circle area is the AUROC added by retina (combined minus clinical only), and open circles mark a lower AUROC with the retina. The strip adds group means with paired bootstrap 95% intervals. One-sided paired bootstrap P, Holm-adjusted over 12 group tests (3 shown), was ≤ 0.012 (the smallest attainable) for eye and other conditions and 1.000 for cardiometabolic and vascular conditions, half with labels clinical inputs may define.
-**c**, Retina and age alone against an age-only ridge and the training median (n ≥ 1,880 with a complete blood count). Paired MAE differences with bootstrap 95% intervals. Open circles mark higher error with the eye. A ridge on raw retinal features was more accurate in six of nine fields (Extended Data Fig. 5). Abbreviations as in Fig. 1.
-**d**, Share of the mean absolute logit contribution by state block for 7 conditions (n withheld by the source), without intervals. Shares are not explained variance.</t>
+          <t>**Fig. 2 | Retinal and clinical data of the same person share information in one BRAN embedding.** **a**, Same-person retrieval between retinal and clinical shared-block states in ≥1,920 AI-READI development participants (point estimates). † Earlier checkpoint, retained model PLACEHOLDER. CCA was not age-adjusted, so the lead over raw CCA holds only before age adjustment. With age removed MRR was 0.049, above all 256 age-matched shuffles (95th percentile 0.020, one-sided permutation *P* ≤ 0.004, the smallest attainable). CCA, canonical correlation analysis. **b**, Native-head AUROC for 26 self-reported conditions from clinical-only and retinal-only inputs in development participants with all three routes (*n* withheld by the source). Circle area, AUROC added by the retina (combined minus clinical only). Open circles, lower AUROC with the retina. Strip, condition-group means. One-sided paired bootstrap *P*, Holm-adjusted over 12 group tests (3 shown), was ≤ 0.012 (the smallest attainable) for eye and other conditions and 1.000 for cardiometabolic and vascular conditions, half with labels clinical inputs may define. **c**, Retina and age alone against an age-only ridge and the training median (*n* ≥ 1,880 with a complete blood count), paired MAE differences. Open circles, higher error with the eye. A ridge on raw retinal features was more accurate in six of nine fields (Extended Data Fig. 5). Abbreviations as in Fig. 1. **d**, Share of the mean absolute logit contribution by state block for 7 conditions (*n* withheld by the source), without intervals. Shares are not explained variance. Intervals (**b**, **c**), 95% paired participant bootstrap (1,000 draws).</t>
         </is>
       </c>
     </row>
@@ -531,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Same-person retrieval in 1,924 AI-READI development participants. Point estimates, no interval was computed.</t>
+          <t>Same-person retrieval in at least 1,920 AI-READI development participants (count floored to 20, proportions rounded to 3 decimals). Point estimates, no interval was computed.</t>
         </is>
       </c>
     </row>
@@ -585,7 +581,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03534303534303534</v>
+        <v>0.035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -618,7 +614,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.002598752598752599</v>
+        <v>0.003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -651,7 +647,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1221413721413721</v>
+        <v>0.122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -684,7 +680,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01299376299376299</v>
+        <v>0.013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -717,7 +713,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.09287903792524324</v>
+        <v>0.093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -750,7 +746,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.05937208593636983</v>
+        <v>0.059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -783,7 +779,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02365019193586031</v>
+        <v>0.024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -816,7 +812,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.04867538488253519</v>
+        <v>0.049</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -849,7 +845,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02027356825907684</v>
+        <v>0.02</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
